--- a/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
+++ b/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -19,11 +19,8 @@
     <sheet name="IFSR-chemicals" sheetId="3" r:id="rId4"/>
     <sheet name="ISFR-ironsteel" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -42,19 +39,85 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Engineering Toolbox</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Methane</t>
+  </si>
+  <si>
+    <t>electricity if</t>
+  </si>
+  <si>
+    <t>hard coal if</t>
+  </si>
+  <si>
+    <t>natural gas if</t>
+  </si>
+  <si>
+    <t>biomass if</t>
+  </si>
+  <si>
+    <t>petroleum diesel if</t>
+  </si>
+  <si>
+    <t>heat if</t>
+  </si>
+  <si>
+    <t>crude oil if</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil if</t>
+  </si>
+  <si>
+    <t>LPG propane or butane if</t>
+  </si>
+  <si>
+    <t>hydrogen if</t>
+  </si>
+  <si>
+    <t>https://www.engineeringtoolbox.com/standard-heat-of-combustion-energy-content-d_1987.html</t>
+  </si>
+  <si>
+    <t>Heat of combustion (energy content) for some common substances</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
     <t>IFSR Industrial Fuel Substitution Ratios</t>
   </si>
   <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>Engineering Toolbox</t>
-  </si>
-  <si>
-    <t>Heat of combustion (energy content) for some common substances</t>
-  </si>
-  <si>
-    <t>https://www.engineeringtoolbox.com/standard-heat-of-combustion-energy-content-d_1987.html</t>
+    <t>Heat of combustion</t>
+  </si>
+  <si>
+    <t>Carbon</t>
+  </si>
+  <si>
+    <t>kJ/mol</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>from Engineering Toolbox</t>
+  </si>
+  <si>
+    <t>mol H2 per mol C (for iron reduction)</t>
+  </si>
+  <si>
+    <t>mol H2 per mol CH4 (for Haber Bosch process)</t>
+  </si>
+  <si>
+    <t>metallurgical coal carbon content</t>
+  </si>
+  <si>
+    <t>natural gas methane content</t>
   </si>
   <si>
     <t>Climate Accountability</t>
@@ -78,7 +141,19 @@
     <t>https://rmi.org/reality-check-natural-gas-true-climate-risk/</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>dmnl</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>from Climate Accountability</t>
+  </si>
+  <si>
+    <t>from RMI</t>
+  </si>
+  <si>
+    <t>H2-coal ratio</t>
   </si>
   <si>
     <t xml:space="preserve">This file defines the BTU of H2 needed to replace one BTU of </t>
@@ -90,6 +165,9 @@
     <t>We calculate this as:</t>
   </si>
   <si>
+    <t>BTU H2/BTU [fuel] = HHV_H2 * 1 / HHV_C * 0.74</t>
+  </si>
+  <si>
     <r>
       <t>BTU</t>
     </r>
@@ -387,18 +465,42 @@
     <t>where HV is the molar heating value (heat of combustion) of the fuel.</t>
   </si>
   <si>
+    <t>Efficiency (dimensionless)</t>
+  </si>
+  <si>
+    <t>electrolysis</t>
+  </si>
+  <si>
+    <t>natural gas reforming</t>
+  </si>
+  <si>
+    <t>coal gasification</t>
+  </si>
+  <si>
+    <t>biomass gasification</t>
+  </si>
+  <si>
+    <t>thermochemical water splitting</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
     <t>In the chemicals sector, the most accessible opportunity for emissions reduction</t>
   </si>
   <si>
     <t>by feedstock substitution is in the production of methanol and ammonia. In these</t>
   </si>
   <si>
+    <t>subsequent product. Natural gas is converted to hydrogen using steam methane</t>
+  </si>
+  <si>
     <t>processes, natural gas or coal is used to produce hydrogen, which is then used to make the</t>
   </si>
   <si>
-    <t>subsequent product. Natural gas is converted to hydrogen using steam methane</t>
-  </si>
-  <si>
     <t>reforming process. Coal is gasified to produce syngas, which is partly hydrogen.</t>
   </si>
   <si>
@@ -417,133 +519,28 @@
     <t>In this case, we have:</t>
   </si>
   <si>
-    <t>BTU H2/BTU [fuel] = HHV_H2 * 1 / HHV_C * 0.74</t>
-  </si>
-  <si>
     <t>where 1 is the ratio of H2 to C in the reaction and 0.74 is the average</t>
   </si>
   <si>
     <t>carbon content of metallurgical coal in the U.S.</t>
   </si>
   <si>
+    <t>In this process, natural gas (or coal) is turned to syngas, and the resulting CO and H2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are used to reduce high-purity iron lumps and pellets in the solid state. </t>
+  </si>
+  <si>
+    <t>We assign the same production efficiency as in the chemicals sector, but note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">that since the final product of SMR going into DRI facilities is syngas, not hydrogen, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">some process emissions remain from the share of CO in the gas that is oxidized to CO2. </t>
+  </si>
+  <si>
     <t>A smaller share of iron is produced globally by the direct reduced iron (DRI) process.</t>
-  </si>
-  <si>
-    <t>In this process, natural gas (or coal) is turned to syngas, and the resulting CO and H2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">are used to reduce high-purity iron lumps and pellets in the solid state. </t>
-  </si>
-  <si>
-    <t>We assign the same production efficiency as in the chemicals sector, but note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">that since the final product of SMR going into DRI facilities is syngas, not hydrogen, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">some process emissions remain from the share of CO in the gas that is oxidized to CO2. </t>
-  </si>
-  <si>
-    <t>Heat of combustion</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Carbon</t>
-  </si>
-  <si>
-    <t>kJ/mol</t>
-  </si>
-  <si>
-    <t>Hydrogen</t>
-  </si>
-  <si>
-    <t>Methane</t>
-  </si>
-  <si>
-    <t>from Engineering Toolbox</t>
-  </si>
-  <si>
-    <t>mol H2 per mol C (for iron reduction)</t>
-  </si>
-  <si>
-    <t>dmnl</t>
-  </si>
-  <si>
-    <t>mol H2 per mol CH4 (for Haber Bosch process)</t>
-  </si>
-  <si>
-    <t>metallurgical coal carbon content</t>
-  </si>
-  <si>
-    <t>from Climate Accountability</t>
-  </si>
-  <si>
-    <t>natural gas methane content</t>
-  </si>
-  <si>
-    <t>from RMI</t>
-  </si>
-  <si>
-    <t>H2-coal ratio</t>
-  </si>
-  <si>
-    <t>Efficiency (dimensionless)</t>
-  </si>
-  <si>
-    <t>electrolysis</t>
-  </si>
-  <si>
-    <t>natural gas reforming</t>
-  </si>
-  <si>
-    <t>coal gasification</t>
-  </si>
-  <si>
-    <t>biomass gasification</t>
-  </si>
-  <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
-    <t>electrolysis with guaranteed clean electricity</t>
-  </si>
-  <si>
-    <t>natural gas reforming with CCS</t>
-  </si>
-  <si>
-    <t>Values</t>
-  </si>
-  <si>
-    <t>electricity if</t>
-  </si>
-  <si>
-    <t>hard coal if</t>
-  </si>
-  <si>
-    <t>natural gas if</t>
-  </si>
-  <si>
-    <t>biomass if</t>
-  </si>
-  <si>
-    <t>petroleum diesel if</t>
-  </si>
-  <si>
-    <t>heat if</t>
-  </si>
-  <si>
-    <t>crude oil if</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil if</t>
-  </si>
-  <si>
-    <t>LPG propane or butane if</t>
-  </si>
-  <si>
-    <t>hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -552,9 +549,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -641,11 +638,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -948,205 +945,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16.5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="16.5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1158,121 +1155,121 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6A4AC5-8865-4921-8E10-BDED8AECA8F6}">
   <dimension ref="A2:C17"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>394</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>286</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>891</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0.74</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>0.8</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6">
         <f>B4*B8*B11/B3</f>
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" s="6"/>
     </row>
   </sheetData>
@@ -1283,15 +1280,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221F3C08-152C-483E-8BAD-E349F8D44D7B}">
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1796875" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B1" s="7">
         <v>2017</v>
@@ -1396,9 +1393,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4">
         <v>0.67045454545454541</v>
@@ -1503,9 +1500,9 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4">
         <v>0.71951219512195119</v>
@@ -1610,9 +1607,9 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4">
         <v>0.57004830917874394</v>
@@ -1717,9 +1714,9 @@
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B5" s="4">
         <v>0.46274509803921571</v>
@@ -1824,9 +1821,9 @@
         <v>0.46274509803921571</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -1931,9 +1928,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B7" s="4">
         <v>0.67045454545454541</v>
@@ -2038,9 +2035,9 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B8" s="4">
         <v>0.71951219512195119</v>
@@ -2156,94 +2153,94 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B3" s="10">
         <f>HPEbP!B4</f>
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B4" s="10">
         <f>HPEbP!B3</f>
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2260,94 +2257,94 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B3" s="10">
         <f>Calcs!B16</f>
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B4" s="10">
         <f>'IFSR-chemicals'!B4</f>
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2356,175 +2353,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47E6F116-417B-44E8-9435-9811EF8CD551}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{413506EC-2F05-4922-B5CD-CFC555125D34}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E32F603A-08E1-4F3E-92AC-EF0C62A8C23C}"/>
 </file>